--- a/templates/SH_GB_Project_Report_Template.xlsx
+++ b/templates/SH_GB_Project_Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AmberShamim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A27BB20-EA59-4949-BBAA-4CF771FADEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22ECD333-6CCC-45B4-81B3-62052CEF4330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
     <sheet name="Template Guide" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Data'!$A$2:$K$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="91">
   <si>
     <t>:candidates:fullname</t>
   </si>
@@ -105,6 +108,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>← Tool populates data from this row downward. Any number of rows.</t>
+  </si>
+  <si>
     <t>_tag</t>
   </si>
   <si>
@@ -114,6 +120,9 @@
     <t>_pct</t>
   </si>
   <si>
+    <t>PROJECT REPORT  ·  {{project_name}}  ·  {{report_date}}</t>
+  </si>
+  <si>
     <t>Total Candidates</t>
   </si>
   <si>
@@ -147,46 +156,91 @@
     <t>Project Name</t>
   </si>
   <si>
+    <t>{{project_name}}</t>
+  </si>
+  <si>
     <t>Assignment Type</t>
   </si>
   <si>
+    <t>{{assignment_type}}</t>
+  </si>
+  <si>
     <t>Client</t>
   </si>
   <si>
+    <t>{{client_name}}</t>
+  </si>
+  <si>
     <t>Lead Consultant</t>
   </si>
   <si>
+    <t>{{lead_consultant}}</t>
+  </si>
+  <si>
     <t>Researcher</t>
   </si>
   <si>
+    <t>{{researcher_name}}</t>
+  </si>
+  <si>
     <t>Date Created</t>
   </si>
   <si>
+    <t>{{date_created}}</t>
+  </si>
+  <si>
     <t>Report Date</t>
   </si>
   <si>
+    <t>{{report_date}}</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
+    <t>{{project_status}}</t>
+  </si>
+  <si>
     <t>Practice</t>
   </si>
   <si>
+    <t>{{practice_area}}</t>
+  </si>
+  <si>
     <t>Geography</t>
   </si>
   <si>
+    <t>{{geography}}</t>
+  </si>
+  <si>
     <t>TOP LOCATIONS</t>
   </si>
   <si>
     <t>%</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
+    <t>{{top_location_1}}</t>
+  </si>
+  <si>
+    <t>{{top_location_2}}</t>
+  </si>
+  <si>
+    <t>{{top_location_3}}</t>
+  </si>
+  <si>
+    <t>{{top_location_4}}</t>
+  </si>
+  <si>
+    <t>{{top_location_5}}</t>
+  </si>
+  <si>
+    <t>{{top_location_6}}</t>
+  </si>
+  <si>
+    <t>{{top_location_7}}</t>
+  </si>
+  <si>
+    <t>{{top_location_8}}</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -283,9 +337,6 @@
   </si>
   <si>
     <t>Fit to Profile</t>
-  </si>
-  <si>
-    <t>PROJECT REPORT  ·</t>
   </si>
 </sst>
 </file>
@@ -295,7 +346,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,6 +365,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FFAAAAAA"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -509,7 +567,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -560,107 +618,122 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC8A96E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC8A96E"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -992,7 +1065,7 @@
   <sheetPr>
     <tabColor rgb="FF1A1A2E"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
@@ -1000,6 +1073,9 @@
     <col min="4" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="9" max="9" width="8.6328125" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" hidden="1">
@@ -1026,42 +1102,47 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>72</v>
+      <c r="H2" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:K3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -1069,18 +1150,438 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A1,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <f>IF(A2="","",COUNTIF('Project Data'!$E$3:$E$10000,A2))</f>
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C31" si="0">IFERROR(B2/SUM($B$2:$B$31),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A2,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <f>IF(A3="","",COUNTIF('Project Data'!$E$3:$E$10000,A3))</f>
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A3,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <f>IF(A4="","",COUNTIF('Project Data'!$E$3:$E$10000,A4))</f>
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A4,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <f>IF(A5="","",COUNTIF('Project Data'!$E$3:$E$10000,A5))</f>
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A5,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <f>IF(A6="","",COUNTIF('Project Data'!$E$3:$E$10000,A6))</f>
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A6,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(A7="","",COUNTIF('Project Data'!$E$3:$E$10000,A7))</f>
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A7,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <f>IF(A8="","",COUNTIF('Project Data'!$E$3:$E$10000,A8))</f>
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A8,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <f>IF(A9="","",COUNTIF('Project Data'!$E$3:$E$10000,A9))</f>
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A9,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <f>IF(A10="","",COUNTIF('Project Data'!$E$3:$E$10000,A10))</f>
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A10,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <f>IF(A11="","",COUNTIF('Project Data'!$E$3:$E$10000,A11))</f>
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A11,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <f>IF(A12="","",COUNTIF('Project Data'!$E$3:$E$10000,A12))</f>
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A12,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B13" t="str">
+        <f>IF(A13="","",COUNTIF('Project Data'!$E$3:$E$10000,A13))</f>
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A13,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <f>IF(A14="","",COUNTIF('Project Data'!$E$3:$E$10000,A14))</f>
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A14,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(A15="","",COUNTIF('Project Data'!$E$3:$E$10000,A15))</f>
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A15,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(A16="","",COUNTIF('Project Data'!$E$3:$E$10000,A16))</f>
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A16,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(A17="","",COUNTIF('Project Data'!$E$3:$E$10000,A17))</f>
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A17,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <f>IF(A18="","",COUNTIF('Project Data'!$E$3:$E$10000,A18))</f>
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A18,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B19" t="str">
+        <f>IF(A19="","",COUNTIF('Project Data'!$E$3:$E$10000,A19))</f>
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A19,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B20" t="str">
+        <f>IF(A20="","",COUNTIF('Project Data'!$E$3:$E$10000,A20))</f>
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A20,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B21" t="str">
+        <f>IF(A21="","",COUNTIF('Project Data'!$E$3:$E$10000,A21))</f>
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A21,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(A22="","",COUNTIF('Project Data'!$E$3:$E$10000,A22))</f>
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A22,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(A23="","",COUNTIF('Project Data'!$E$3:$E$10000,A23))</f>
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A23,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(A24="","",COUNTIF('Project Data'!$E$3:$E$10000,A24))</f>
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A24,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(A25="","",COUNTIF('Project Data'!$E$3:$E$10000,A25))</f>
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A25,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <f>IF(A26="","",COUNTIF('Project Data'!$E$3:$E$10000,A26))</f>
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A26,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <f>IF(A27="","",COUNTIF('Project Data'!$E$3:$E$10000,A27))</f>
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A27,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <f>IF(A28="","",COUNTIF('Project Data'!$E$3:$E$10000,A28))</f>
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A28,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <f>IF(A29="","",COUNTIF('Project Data'!$E$3:$E$10000,A29))</f>
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A29,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(A30="","",COUNTIF('Project Data'!$E$3:$E$10000,A30))</f>
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="str">
+        <f>IFERROR(INDEX('Project Data'!$E$3:$E$10000,MATCH(0,COUNTIF($A$1:A30,'Project Data'!$E$3:$E$10000)+(('Project Data'!$E$3:$E$10000)=""),0)),"")</f>
+        <v/>
+      </c>
+      <c r="B31" t="str">
+        <f>IF(A31="","",COUNTIF('Project Data'!$E$3:$E$10000,A31))</f>
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1106,1014 +1607,1044 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A1" s="21" t="e" vm="1">
+      <c r="A1" s="22" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
+      <c r="A2" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
     </row>
     <row r="3" spans="1:10" ht="3" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:10" ht="7.5" customHeight="1"/>
     <row r="5" spans="1:10" ht="18" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A6" s="25">
+      <c r="A6" s="26">
         <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
-        <v>0</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26">
         <f>COUNTIF(_Pivot!B2:B31,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Interview*")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25">
+      <c r="F6" s="26"/>
+      <c r="G6" s="26">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Offer*")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25">
+      <c r="H6" s="26"/>
+      <c r="I6" s="26">
         <f>COUNTIF('Project Data'!$E$3:$E$10000,"*Placed*")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
     </row>
     <row r="9" spans="1:10" ht="3.75" customHeight="1">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
     </row>
     <row r="10" spans="1:10" ht="9.75" customHeight="1"/>
     <row r="11" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A11" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="F11" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
+      <c r="A11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="F11" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
     <row r="12" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="D12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="29"/>
+      <c r="H12" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="5" t="str">
+      <c r="A13" s="6" t="str">
         <f>IF(_Pivot!A2="","",_Pivot!A2)</f>
         <v/>
       </c>
-      <c r="B13" s="6" t="str">
+      <c r="B13" s="7" t="str">
         <f>IF(A13="","",_Pivot!B2)</f>
         <v/>
       </c>
-      <c r="C13" s="7" t="str">
+      <c r="C13" s="8" t="str">
         <f>IF(A13="","",_Pivot!C2)</f>
         <v/>
       </c>
-      <c r="D13" s="8" t="str">
+      <c r="D13" s="9" t="str">
         <f t="shared" ref="D13:D42" si="0">IF(A13="","",IFERROR(REPT("█",ROUND(C13*25,0)),""))</f>
         <v/>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
+      <c r="F13" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="9" t="str">
+      <c r="A14" s="10" t="str">
         <f>IF(_Pivot!A3="","",_Pivot!A3)</f>
         <v/>
       </c>
-      <c r="B14" s="10" t="str">
+      <c r="B14" s="11" t="str">
         <f>IF(A14="","",_Pivot!B3)</f>
         <v/>
       </c>
-      <c r="C14" s="11" t="str">
+      <c r="C14" s="12" t="str">
         <f>IF(A14="","",_Pivot!C3)</f>
         <v/>
       </c>
-      <c r="D14" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
+      <c r="D14" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="5" t="str">
+      <c r="A15" s="6" t="str">
         <f>IF(_Pivot!A4="","",_Pivot!A4)</f>
         <v/>
       </c>
-      <c r="B15" s="6" t="str">
+      <c r="B15" s="7" t="str">
         <f>IF(A15="","",_Pivot!B4)</f>
         <v/>
       </c>
-      <c r="C15" s="7" t="str">
+      <c r="C15" s="8" t="str">
         <f>IF(A15="","",_Pivot!C4)</f>
         <v/>
       </c>
-      <c r="D15" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
+      <c r="D15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="9" t="str">
+      <c r="A16" s="10" t="str">
         <f>IF(_Pivot!A5="","",_Pivot!A5)</f>
         <v/>
       </c>
-      <c r="B16" s="10" t="str">
+      <c r="B16" s="11" t="str">
         <f>IF(A16="","",_Pivot!B5)</f>
         <v/>
       </c>
-      <c r="C16" s="11" t="str">
+      <c r="C16" s="12" t="str">
         <f>IF(A16="","",_Pivot!C5)</f>
         <v/>
       </c>
-      <c r="D16" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
+      <c r="D16" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="5" t="str">
+      <c r="A17" s="6" t="str">
         <f>IF(_Pivot!A6="","",_Pivot!A6)</f>
         <v/>
       </c>
-      <c r="B17" s="6" t="str">
+      <c r="B17" s="7" t="str">
         <f>IF(A17="","",_Pivot!B6)</f>
         <v/>
       </c>
-      <c r="C17" s="7" t="str">
+      <c r="C17" s="8" t="str">
         <f>IF(A17="","",_Pivot!C6)</f>
         <v/>
       </c>
-      <c r="D17" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
+      <c r="D17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="9" t="str">
+      <c r="A18" s="10" t="str">
         <f>IF(_Pivot!A7="","",_Pivot!A7)</f>
         <v/>
       </c>
-      <c r="B18" s="10" t="str">
+      <c r="B18" s="11" t="str">
         <f>IF(A18="","",_Pivot!B7)</f>
         <v/>
       </c>
-      <c r="C18" s="11" t="str">
+      <c r="C18" s="12" t="str">
         <f>IF(A18="","",_Pivot!C7)</f>
         <v/>
       </c>
-      <c r="D18" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
+      <c r="D18" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="5" t="str">
+      <c r="A19" s="6" t="str">
         <f>IF(_Pivot!A8="","",_Pivot!A8)</f>
         <v/>
       </c>
-      <c r="B19" s="6" t="str">
+      <c r="B19" s="7" t="str">
         <f>IF(A19="","",_Pivot!B8)</f>
         <v/>
       </c>
-      <c r="C19" s="7" t="str">
+      <c r="C19" s="8" t="str">
         <f>IF(A19="","",_Pivot!C8)</f>
         <v/>
       </c>
-      <c r="D19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
+      <c r="D19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="29"/>
+      <c r="H19" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="9" t="str">
+      <c r="A20" s="10" t="str">
         <f>IF(_Pivot!A9="","",_Pivot!A9)</f>
         <v/>
       </c>
-      <c r="B20" s="10" t="str">
+      <c r="B20" s="11" t="str">
         <f>IF(A20="","",_Pivot!B9)</f>
         <v/>
       </c>
-      <c r="C20" s="11" t="str">
+      <c r="C20" s="12" t="str">
         <f>IF(A20="","",_Pivot!C9)</f>
         <v/>
       </c>
-      <c r="D20" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
+      <c r="D20" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="29"/>
+      <c r="H20" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="5" t="str">
+      <c r="A21" s="6" t="str">
         <f>IF(_Pivot!A10="","",_Pivot!A10)</f>
         <v/>
       </c>
-      <c r="B21" s="6" t="str">
+      <c r="B21" s="7" t="str">
         <f>IF(A21="","",_Pivot!B10)</f>
         <v/>
       </c>
-      <c r="C21" s="7" t="str">
+      <c r="C21" s="8" t="str">
         <f>IF(A21="","",_Pivot!C10)</f>
         <v/>
       </c>
-      <c r="D21" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
+      <c r="D21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1">
-      <c r="A22" s="9" t="str">
+      <c r="A22" s="10" t="str">
         <f>IF(_Pivot!A11="","",_Pivot!A11)</f>
         <v/>
       </c>
-      <c r="B22" s="10" t="str">
+      <c r="B22" s="11" t="str">
         <f>IF(A22="","",_Pivot!B11)</f>
         <v/>
       </c>
-      <c r="C22" s="11" t="str">
+      <c r="C22" s="12" t="str">
         <f>IF(A22="","",_Pivot!C11)</f>
         <v/>
       </c>
-      <c r="D22" s="12" t="str">
+      <c r="D22" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1">
-      <c r="A23" s="5" t="str">
+      <c r="A23" s="6" t="str">
         <f>IF(_Pivot!A12="","",_Pivot!A12)</f>
         <v/>
       </c>
-      <c r="B23" s="6" t="str">
+      <c r="B23" s="7" t="str">
         <f>IF(A23="","",_Pivot!B12)</f>
         <v/>
       </c>
-      <c r="C23" s="7" t="str">
+      <c r="C23" s="8" t="str">
         <f>IF(A23="","",_Pivot!C12)</f>
         <v/>
       </c>
-      <c r="D23" s="8" t="str">
+      <c r="D23" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1">
-      <c r="A24" s="9" t="str">
+      <c r="A24" s="10" t="str">
         <f>IF(_Pivot!A13="","",_Pivot!A13)</f>
         <v/>
       </c>
-      <c r="B24" s="10" t="str">
+      <c r="B24" s="11" t="str">
         <f>IF(A24="","",_Pivot!B13)</f>
         <v/>
       </c>
-      <c r="C24" s="11" t="str">
+      <c r="C24" s="12" t="str">
         <f>IF(A24="","",_Pivot!C13)</f>
         <v/>
       </c>
-      <c r="D24" s="12" t="str">
+      <c r="D24" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1">
-      <c r="A25" s="5" t="str">
+      <c r="A25" s="6" t="str">
         <f>IF(_Pivot!A14="","",_Pivot!A14)</f>
         <v/>
       </c>
-      <c r="B25" s="6" t="str">
+      <c r="B25" s="7" t="str">
         <f>IF(A25="","",_Pivot!B14)</f>
         <v/>
       </c>
-      <c r="C25" s="7" t="str">
+      <c r="C25" s="8" t="str">
         <f>IF(A25="","",_Pivot!C14)</f>
         <v/>
       </c>
-      <c r="D25" s="8" t="str">
+      <c r="D25" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="9" t="str">
+      <c r="A26" s="10" t="str">
         <f>IF(_Pivot!A15="","",_Pivot!A15)</f>
         <v/>
       </c>
-      <c r="B26" s="10" t="str">
+      <c r="B26" s="11" t="str">
         <f>IF(A26="","",_Pivot!B15)</f>
         <v/>
       </c>
-      <c r="C26" s="11" t="str">
+      <c r="C26" s="12" t="str">
         <f>IF(A26="","",_Pivot!C15)</f>
         <v/>
       </c>
-      <c r="D26" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
+      <c r="D26" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="5" t="str">
+      <c r="A27" s="6" t="str">
         <f>IF(_Pivot!A16="","",_Pivot!A16)</f>
         <v/>
       </c>
-      <c r="B27" s="6" t="str">
+      <c r="B27" s="7" t="str">
         <f>IF(A27="","",_Pivot!B16)</f>
         <v/>
       </c>
-      <c r="C27" s="7" t="str">
+      <c r="C27" s="8" t="str">
         <f>IF(A27="","",_Pivot!C16)</f>
         <v/>
       </c>
-      <c r="D27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="D27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>38</v>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1">
-      <c r="A28" s="9" t="str">
+      <c r="A28" s="10" t="str">
         <f>IF(_Pivot!A17="","",_Pivot!A17)</f>
         <v/>
       </c>
-      <c r="B28" s="10" t="str">
+      <c r="B28" s="11" t="str">
         <f>IF(A28="","",_Pivot!B17)</f>
         <v/>
       </c>
-      <c r="C28" s="11" t="str">
+      <c r="C28" s="12" t="str">
         <f>IF(A28="","",_Pivot!C17)</f>
         <v/>
       </c>
-      <c r="D28" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="6" t="str">
+      <c r="D28" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="7">
         <f>IF(F28="","",COUNTIF('Project Data'!$D$3:$D$10000,F28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8" t="str">
         <f t="shared" ref="J28:J35" si="1">IFERROR(I28/SUM($I$28:$I$35),"")</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1">
-      <c r="A29" s="5" t="str">
+      <c r="A29" s="6" t="str">
         <f>IF(_Pivot!A18="","",_Pivot!A18)</f>
         <v/>
       </c>
-      <c r="B29" s="6" t="str">
+      <c r="B29" s="7" t="str">
         <f>IF(A29="","",_Pivot!B18)</f>
         <v/>
       </c>
-      <c r="C29" s="7" t="str">
+      <c r="C29" s="8" t="str">
         <f>IF(A29="","",_Pivot!C18)</f>
         <v/>
       </c>
-      <c r="D29" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="10" t="str">
+      <c r="D29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="11">
         <f>IF(F29="","",COUNTIF('Project Data'!$D$3:$D$10000,F29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1">
-      <c r="A30" s="9" t="str">
+      <c r="A30" s="10" t="str">
         <f>IF(_Pivot!A19="","",_Pivot!A19)</f>
         <v/>
       </c>
-      <c r="B30" s="10" t="str">
+      <c r="B30" s="11" t="str">
         <f>IF(A30="","",_Pivot!B19)</f>
         <v/>
       </c>
-      <c r="C30" s="11" t="str">
+      <c r="C30" s="12" t="str">
         <f>IF(A30="","",_Pivot!C19)</f>
         <v/>
       </c>
-      <c r="D30" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="6" t="str">
+      <c r="D30" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="7">
         <f>IF(F30="","",COUNTIF('Project Data'!$D$3:$D$10000,F30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1">
-      <c r="A31" s="5" t="str">
+      <c r="A31" s="6" t="str">
         <f>IF(_Pivot!A20="","",_Pivot!A20)</f>
         <v/>
       </c>
-      <c r="B31" s="6" t="str">
+      <c r="B31" s="7" t="str">
         <f>IF(A31="","",_Pivot!B20)</f>
         <v/>
       </c>
-      <c r="C31" s="7" t="str">
+      <c r="C31" s="8" t="str">
         <f>IF(A31="","",_Pivot!C20)</f>
         <v/>
       </c>
-      <c r="D31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="10" t="str">
+      <c r="D31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="11">
         <f>IF(F31="","",COUNTIF('Project Data'!$D$3:$D$10000,F31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="J31" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1">
-      <c r="A32" s="9" t="str">
+      <c r="A32" s="10" t="str">
         <f>IF(_Pivot!A21="","",_Pivot!A21)</f>
         <v/>
       </c>
-      <c r="B32" s="10" t="str">
+      <c r="B32" s="11" t="str">
         <f>IF(A32="","",_Pivot!B21)</f>
         <v/>
       </c>
-      <c r="C32" s="11" t="str">
+      <c r="C32" s="12" t="str">
         <f>IF(A32="","",_Pivot!C21)</f>
         <v/>
       </c>
-      <c r="D32" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="6" t="str">
+      <c r="D32" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="7">
         <f>IF(F32="","",COUNTIF('Project Data'!$D$3:$D$10000,F32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:10" ht="18" customHeight="1">
-      <c r="A33" s="5" t="str">
+      <c r="A33" s="6" t="str">
         <f>IF(_Pivot!A22="","",_Pivot!A22)</f>
         <v/>
       </c>
-      <c r="B33" s="6" t="str">
+      <c r="B33" s="7" t="str">
         <f>IF(A33="","",_Pivot!B22)</f>
         <v/>
       </c>
-      <c r="C33" s="7" t="str">
+      <c r="C33" s="8" t="str">
         <f>IF(A33="","",_Pivot!C22)</f>
         <v/>
       </c>
-      <c r="D33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F33" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="10" t="str">
+      <c r="D33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="11">
         <f>IF(F33="","",COUNTIF('Project Data'!$D$3:$D$10000,F33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1">
-      <c r="A34" s="9" t="str">
+      <c r="A34" s="10" t="str">
         <f>IF(_Pivot!A23="","",_Pivot!A23)</f>
         <v/>
       </c>
-      <c r="B34" s="10" t="str">
+      <c r="B34" s="11" t="str">
         <f>IF(A34="","",_Pivot!B23)</f>
         <v/>
       </c>
-      <c r="C34" s="11" t="str">
+      <c r="C34" s="12" t="str">
         <f>IF(A34="","",_Pivot!C23)</f>
         <v/>
       </c>
-      <c r="D34" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="6" t="str">
+      <c r="D34" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="7">
         <f>IF(F34="","",COUNTIF('Project Data'!$D$3:$D$10000,F34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:10" ht="18" customHeight="1">
-      <c r="A35" s="5" t="str">
+      <c r="A35" s="6" t="str">
         <f>IF(_Pivot!A24="","",_Pivot!A24)</f>
         <v/>
       </c>
-      <c r="B35" s="6" t="str">
+      <c r="B35" s="7" t="str">
         <f>IF(A35="","",_Pivot!B24)</f>
         <v/>
       </c>
-      <c r="C35" s="7" t="str">
+      <c r="C35" s="8" t="str">
         <f>IF(A35="","",_Pivot!C24)</f>
         <v/>
       </c>
-      <c r="D35" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F35" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="10" t="str">
+      <c r="D35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="11">
         <f>IF(F35="","",COUNTIF('Project Data'!$D$3:$D$10000,F35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1">
-      <c r="A36" s="9" t="str">
+      <c r="A36" s="10" t="str">
         <f>IF(_Pivot!A25="","",_Pivot!A25)</f>
         <v/>
       </c>
-      <c r="B36" s="10" t="str">
+      <c r="B36" s="11" t="str">
         <f>IF(A36="","",_Pivot!B25)</f>
         <v/>
       </c>
-      <c r="C36" s="11" t="str">
+      <c r="C36" s="12" t="str">
         <f>IF(A36="","",_Pivot!C25)</f>
         <v/>
       </c>
-      <c r="D36" s="12" t="str">
+      <c r="D36" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1">
-      <c r="A37" s="5" t="str">
+      <c r="A37" s="6" t="str">
         <f>IF(_Pivot!A26="","",_Pivot!A26)</f>
         <v/>
       </c>
-      <c r="B37" s="6" t="str">
+      <c r="B37" s="7" t="str">
         <f>IF(A37="","",_Pivot!B26)</f>
         <v/>
       </c>
-      <c r="C37" s="7" t="str">
+      <c r="C37" s="8" t="str">
         <f>IF(A37="","",_Pivot!C26)</f>
         <v/>
       </c>
-      <c r="D37" s="8" t="str">
+      <c r="D37" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1">
-      <c r="A38" s="9" t="str">
+      <c r="A38" s="10" t="str">
         <f>IF(_Pivot!A27="","",_Pivot!A27)</f>
         <v/>
       </c>
-      <c r="B38" s="10" t="str">
+      <c r="B38" s="11" t="str">
         <f>IF(A38="","",_Pivot!B27)</f>
         <v/>
       </c>
-      <c r="C38" s="11" t="str">
+      <c r="C38" s="12" t="str">
         <f>IF(A38="","",_Pivot!C27)</f>
         <v/>
       </c>
-      <c r="D38" s="12" t="str">
+      <c r="D38" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:10" ht="18" customHeight="1">
-      <c r="A39" s="5" t="str">
+      <c r="A39" s="6" t="str">
         <f>IF(_Pivot!A28="","",_Pivot!A28)</f>
         <v/>
       </c>
-      <c r="B39" s="6" t="str">
+      <c r="B39" s="7" t="str">
         <f>IF(A39="","",_Pivot!B28)</f>
         <v/>
       </c>
-      <c r="C39" s="7" t="str">
+      <c r="C39" s="8" t="str">
         <f>IF(A39="","",_Pivot!C28)</f>
         <v/>
       </c>
-      <c r="D39" s="8" t="str">
+      <c r="D39" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="1:10" ht="18" customHeight="1">
-      <c r="A40" s="9" t="str">
+      <c r="A40" s="10" t="str">
         <f>IF(_Pivot!A29="","",_Pivot!A29)</f>
         <v/>
       </c>
-      <c r="B40" s="10" t="str">
+      <c r="B40" s="11" t="str">
         <f>IF(A40="","",_Pivot!B29)</f>
         <v/>
       </c>
-      <c r="C40" s="11" t="str">
+      <c r="C40" s="12" t="str">
         <f>IF(A40="","",_Pivot!C29)</f>
         <v/>
       </c>
-      <c r="D40" s="12" t="str">
+      <c r="D40" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1">
-      <c r="A41" s="5" t="str">
+      <c r="A41" s="6" t="str">
         <f>IF(_Pivot!A30="","",_Pivot!A30)</f>
         <v/>
       </c>
-      <c r="B41" s="6" t="str">
+      <c r="B41" s="7" t="str">
         <f>IF(A41="","",_Pivot!B30)</f>
         <v/>
       </c>
-      <c r="C41" s="7" t="str">
+      <c r="C41" s="8" t="str">
         <f>IF(A41="","",_Pivot!C30)</f>
         <v/>
       </c>
-      <c r="D41" s="8" t="str">
+      <c r="D41" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1">
-      <c r="A42" s="9" t="str">
+      <c r="A42" s="10" t="str">
         <f>IF(_Pivot!A31="","",_Pivot!A31)</f>
         <v/>
       </c>
-      <c r="B42" s="10" t="str">
+      <c r="B42" s="11" t="str">
         <f>IF(A42="","",_Pivot!B31)</f>
         <v/>
       </c>
-      <c r="C42" s="11" t="str">
+      <c r="C42" s="12" t="str">
         <f>IF(A42="","",_Pivot!C31)</f>
         <v/>
       </c>
-      <c r="D42" s="12" t="str">
+      <c r="D42" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A43" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="14">
+      <c r="A43" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="15">
         <f>COUNTA('Project Data'!$A$3:$A$10000)</f>
-        <v>0</v>
-      </c>
-      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="C43" s="16">
         <f>IFERROR(SUM(C13:C42),"")</f>
         <v>0</v>
       </c>
-      <c r="D43" s="16"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44" spans="1:10" ht="9.75" customHeight="1"/>
     <row r="45" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A45" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
+      <c r="A45" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>44</v>
+      <c r="B46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="18" customHeight="1">
-      <c r="A47" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="6">
+      <c r="A47" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="7">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Male")</f>
         <v>0</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="8">
         <f>IFERROR(B47/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D47" s="8" t="str">
+      <c r="D47" s="9" t="str">
         <f>IFERROR(REPT("█",ROUND(C47*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:10" ht="18" customHeight="1">
-      <c r="A48" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="10">
+      <c r="A48" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="11">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Female")</f>
         <v>0</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="12">
         <f>IFERROR(B48/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D48" s="12" t="str">
+      <c r="D48" s="13" t="str">
         <f>IFERROR(REPT("█",ROUND(C48*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:10" ht="18" customHeight="1">
-      <c r="A49" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="6">
+      <c r="A49" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="7">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Non-Binary*")</f>
         <v>0</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <f>IFERROR(B49/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="8" t="str">
+      <c r="D49" s="9" t="str">
         <f>IFERROR(REPT("█",ROUND(C49*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:10" ht="18" customHeight="1">
-      <c r="A50" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="10">
+      <c r="A50" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="11">
         <f>COUNTIF('Project Data'!$F$3:$F$10000,"Not Specified")</f>
         <v>0</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="12">
         <f>IFERROR(B50/SUM(B47:B50),0)</f>
         <v>0</v>
       </c>
-      <c r="D50" s="12" t="str">
+      <c r="D50" s="13" t="str">
         <f>IFERROR(REPT("█",ROUND(C50*20,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:10" ht="9.75" customHeight="1"/>
     <row r="54" spans="1:10" ht="3" customHeight="1">
-      <c r="A54" s="33"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
     </row>
     <row r="55" spans="1:10" ht="18" customHeight="1">
-      <c r="A55" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
+      <c r="A55" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -2185,115 +2716,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="A1" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A2" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="A2" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>52</v>
+      <c r="A3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>54</v>
+      <c r="A4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>56</v>
+      <c r="A5" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="19"/>
-      <c r="B6" s="18"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="19"/>
     </row>
     <row r="7" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A7" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="A7" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>59</v>
+      <c r="A8" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>61</v>
+      <c r="A9" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>63</v>
+      <c r="A10" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="18"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="19"/>
     </row>
     <row r="12" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A12" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="A12" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>66</v>
+      <c r="A13" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>68</v>
+      <c r="A14" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
